--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.90997673480535</v>
+        <v>8.435371219405869</v>
       </c>
       <c r="D2" t="n">
-        <v>52.25162613858752</v>
+        <v>8.490889247520473</v>
       </c>
       <c r="E2" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F2" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.26316133904866</v>
+        <v>6.705263717595408</v>
       </c>
       <c r="D3" t="n">
-        <v>41.35298777879704</v>
+        <v>6.719860514054519</v>
       </c>
       <c r="E3" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F3" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.73003418058833</v>
+        <v>8.081130554345604</v>
       </c>
       <c r="D4" t="n">
-        <v>49.32087829427364</v>
+        <v>8.014642722819467</v>
       </c>
       <c r="E4" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F4" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.60228983854446</v>
+        <v>8.872872098763477</v>
       </c>
       <c r="D5" t="n">
-        <v>54.10800756156246</v>
+        <v>8.792551228753901</v>
       </c>
       <c r="E5" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F5" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.00734094086912</v>
+        <v>5.038692902891233</v>
       </c>
       <c r="D6" t="n">
-        <v>30.57171500984299</v>
+        <v>4.967903689099486</v>
       </c>
       <c r="E6" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F6" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1.653999614189577</v>
+        <v>0.2687749373058063</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9371108422790334</v>
+        <v>0.1522805118703429</v>
       </c>
       <c r="E7" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F7" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.76188195326311</v>
+        <v>6.623805817405255</v>
       </c>
       <c r="D8" t="n">
-        <v>41.4163348092859</v>
+        <v>6.730154406508959</v>
       </c>
       <c r="E8" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F8" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.12277468096959</v>
+        <v>4.407450885657559</v>
       </c>
       <c r="D9" t="n">
-        <v>26.4571439123158</v>
+        <v>4.299285885751317</v>
       </c>
       <c r="E9" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F9" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90010589234716</v>
+        <v>4.533767207506414</v>
       </c>
       <c r="D10" t="n">
-        <v>27.92289874716899</v>
+        <v>4.537471046414961</v>
       </c>
       <c r="E10" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F10" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.09647124601312</v>
+        <v>2.453176577477133</v>
       </c>
       <c r="D11" t="n">
-        <v>14.98150115033133</v>
+        <v>2.434493936928841</v>
       </c>
       <c r="E11" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F11" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.25312339962922</v>
+        <v>7.841132552439748</v>
       </c>
       <c r="D12" t="n">
-        <v>47.92652826729677</v>
+        <v>7.788060843435725</v>
       </c>
       <c r="E12" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F12" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.47165386209217</v>
+        <v>5.276643752589978</v>
       </c>
       <c r="D13" t="n">
-        <v>32.57883287450386</v>
+        <v>5.294060342106877</v>
       </c>
       <c r="E13" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F13" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.50750750203917</v>
+        <v>1.707469969081366</v>
       </c>
       <c r="D14" t="n">
-        <v>10.51877219259769</v>
+        <v>1.709300481297125</v>
       </c>
       <c r="E14" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F14" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.23454961100207</v>
+        <v>6.375614311787836</v>
       </c>
       <c r="D15" t="n">
-        <v>38.8365287373401</v>
+        <v>6.310935919817767</v>
       </c>
       <c r="E15" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F15" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>6.54832313998156</v>
+        <v>1.064102510247003</v>
       </c>
       <c r="D16" t="n">
-        <v>6.128833594302558</v>
+        <v>0.9959354590741658</v>
       </c>
       <c r="E16" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F16" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>30.33494365504167</v>
+        <v>4.929428343944272</v>
       </c>
       <c r="D17" t="n">
-        <v>30.49226202931867</v>
+        <v>4.954992579764284</v>
       </c>
       <c r="E17" t="n">
-        <v>15.93109033456573</v>
+        <v>2.588802179366931</v>
       </c>
       <c r="F17" t="n">
-        <v>16.02796284420179</v>
+        <v>2.604543962182791</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
